--- a/excel-files/CALOOCAN/MAYPAJO HIGH SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/MAYPAJO HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817FF042-EA5A-4B84-9849-C1986E0CAAB5}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D246872A-8A4D-41ED-B480-3AAF2155D611}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -767,6 +767,12 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -778,12 +784,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3562,7 +3562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:8" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:8" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3772,7 +3772,7 @@
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:8" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3902,7 +3902,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:8" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -5567,11 +5567,11 @@
       <c r="F98" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G98" s="46">
+      <c r="G98" s="42">
         <f>IF((C98-D98)&lt;0,0,C98-D98)</f>
         <v>95</v>
       </c>
-      <c r="H98" s="47">
+      <c r="H98" s="43">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
@@ -5595,11 +5595,11 @@
       <c r="F99" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G99" s="46">
+      <c r="G99" s="42">
         <f>IF((C99-D99)&lt;0,0,C99-D99)</f>
         <v>61</v>
       </c>
-      <c r="H99" s="47">
+      <c r="H99" s="43">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
@@ -5623,11 +5623,11 @@
       <c r="F100" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G100" s="46">
+      <c r="G100" s="42">
         <f t="shared" ref="G100:H100" si="20">IF((C100-D100)&lt;0,0,C100-D100)</f>
         <v>95</v>
       </c>
-      <c r="H100" s="46">
+      <c r="H100" s="42">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -5639,8 +5639,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E100" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E100 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F100" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5685,38 +5685,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5801,7 +5801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" hidden="1" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>63</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6461,7 +6461,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -7035,7 +7035,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7678,7 +7678,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8321,7 +8321,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8964,7 +8964,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -14640,15 +14640,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{B2EA8AE7-6856-48DC-9E02-2A6828EEA4A2}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14663,7 +14666,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14693,38 +14696,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14809,7 +14812,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14878,7 +14881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" ht="19.149999999999999">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14947,7 +14950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -15016,7 +15019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -15085,7 +15088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -15154,7 +15157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -15223,7 +15226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -15292,7 +15295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -15362,7 +15365,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -15431,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -15500,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -15569,7 +15572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15638,7 +15641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15707,7 +15710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15776,7 +15779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15845,7 +15848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15915,7 +15918,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15984,7 +15987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -16122,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -16191,7 +16194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -16260,7 +16263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -16329,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -16398,7 +16401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -16467,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -16537,7 +16540,7 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -16606,7 +16609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16675,7 +16678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16744,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16813,7 +16816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16882,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16951,7 +16954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -17020,7 +17023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -17089,7 +17092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -17158,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -17227,7 +17230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -17297,7 +17300,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -17366,7 +17369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -17435,7 +17438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -17504,7 +17507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -17573,7 +17576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17642,7 +17645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17711,7 +17714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17780,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17849,7 +17852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17918,7 +17921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17987,7 +17990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -18057,7 +18060,7 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -18126,7 +18129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -18195,7 +18198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -18264,7 +18267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -18333,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -18402,7 +18405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -18471,7 +18474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -18540,7 +18543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -18609,7 +18612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18678,7 +18681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18747,7 +18750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -23094,186 +23097,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -23287,12 +23110,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{4E2576EA-8E52-46B9-BDC3-4FD3A709C6A1}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
